--- a/artfynd/A 46181-2023 artfynd.xlsx
+++ b/artfynd/A 46181-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46181-2023 artfynd.xlsx
+++ b/artfynd/A 46181-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2356,6 +2356,210 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122843743</v>
+      </c>
+      <c r="B16" t="n">
+        <v>105453</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vidflagen, Vidflagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>584254</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6321150</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122843907</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vidflagen, Vidflagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>584245</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6321189</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46181-2023 artfynd.xlsx
+++ b/artfynd/A 46181-2023 artfynd.xlsx
@@ -2361,7 +2361,7 @@
         <v>122843743</v>
       </c>
       <c r="B16" t="n">
-        <v>105453</v>
+        <v>105461</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>122843907</v>
       </c>
       <c r="B17" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 46181-2023 artfynd.xlsx
+++ b/artfynd/A 46181-2023 artfynd.xlsx
@@ -2358,10 +2358,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122843743</v>
+        <v>122843907</v>
       </c>
       <c r="B16" t="n">
-        <v>105461</v>
+        <v>98355</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2370,25 +2370,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584254</v>
+        <v>584245</v>
       </c>
       <c r="R16" t="n">
-        <v>6321150</v>
+        <v>6321189</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122843907</v>
+        <v>122843743</v>
       </c>
       <c r="B17" t="n">
-        <v>98355</v>
+        <v>105461</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2472,25 +2472,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584245</v>
+        <v>584254</v>
       </c>
       <c r="R17" t="n">
-        <v>6321189</v>
+        <v>6321150</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>

--- a/artfynd/A 46181-2023 artfynd.xlsx
+++ b/artfynd/A 46181-2023 artfynd.xlsx
@@ -2361,7 +2361,7 @@
         <v>122843907</v>
       </c>
       <c r="B16" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>122843743</v>
       </c>
       <c r="B17" t="n">
-        <v>105461</v>
+        <v>105463</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 46181-2023 artfynd.xlsx
+++ b/artfynd/A 46181-2023 artfynd.xlsx
@@ -2361,7 +2361,7 @@
         <v>122843907</v>
       </c>
       <c r="B16" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>122843743</v>
       </c>
       <c r="B17" t="n">
-        <v>105463</v>
+        <v>105471</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 46181-2023 artfynd.xlsx
+++ b/artfynd/A 46181-2023 artfynd.xlsx
@@ -2358,10 +2358,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122843907</v>
+        <v>122843743</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2370,25 +2370,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584245</v>
+        <v>584254</v>
       </c>
       <c r="R16" t="n">
-        <v>6321189</v>
+        <v>6321150</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122843743</v>
+        <v>122843907</v>
       </c>
       <c r="B17" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2472,25 +2472,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584254</v>
+        <v>584245</v>
       </c>
       <c r="R17" t="n">
-        <v>6321150</v>
+        <v>6321189</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>

--- a/artfynd/A 46181-2023 artfynd.xlsx
+++ b/artfynd/A 46181-2023 artfynd.xlsx
@@ -2361,7 +2361,7 @@
         <v>122843743</v>
       </c>
       <c r="B16" t="n">
-        <v>105471</v>
+        <v>105474</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>122843907</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 46181-2023 artfynd.xlsx
+++ b/artfynd/A 46181-2023 artfynd.xlsx
@@ -2361,7 +2361,7 @@
         <v>122843743</v>
       </c>
       <c r="B16" t="n">
-        <v>105474</v>
+        <v>105476</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>122843907</v>
       </c>
       <c r="B17" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 46181-2023 artfynd.xlsx
+++ b/artfynd/A 46181-2023 artfynd.xlsx
@@ -2358,10 +2358,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122843743</v>
+        <v>122843907</v>
       </c>
       <c r="B16" t="n">
-        <v>105476</v>
+        <v>98376</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2370,25 +2370,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584254</v>
+        <v>584245</v>
       </c>
       <c r="R16" t="n">
-        <v>6321150</v>
+        <v>6321189</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122843907</v>
+        <v>122843743</v>
       </c>
       <c r="B17" t="n">
-        <v>98370</v>
+        <v>105482</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2472,25 +2472,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584245</v>
+        <v>584254</v>
       </c>
       <c r="R17" t="n">
-        <v>6321189</v>
+        <v>6321150</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>

--- a/artfynd/A 46181-2023 artfynd.xlsx
+++ b/artfynd/A 46181-2023 artfynd.xlsx
@@ -2565,7 +2565,7 @@
         <v>122844065</v>
       </c>
       <c r="B18" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 46181-2023 artfynd.xlsx
+++ b/artfynd/A 46181-2023 artfynd.xlsx
@@ -2565,7 +2565,7 @@
         <v>122844065</v>
       </c>
       <c r="B18" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 46181-2023 artfynd.xlsx
+++ b/artfynd/A 46181-2023 artfynd.xlsx
@@ -2565,7 +2565,7 @@
         <v>122844065</v>
       </c>
       <c r="B18" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 46181-2023 artfynd.xlsx
+++ b/artfynd/A 46181-2023 artfynd.xlsx
@@ -2565,7 +2565,7 @@
         <v>122844065</v>
       </c>
       <c r="B18" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
